--- a/outputs/results/pacdemons_all_phases.xlsx
+++ b/outputs/results/pacdemons_all_phases.xlsx
@@ -2,16 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All cells" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All cells'!$B$1:$B$56</definedName>
-  </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -27,63 +26,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -91,51 +45,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -498,35 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" style="13" min="1" max="1"/>
-    <col width="36" customWidth="1" style="13" min="2" max="2"/>
-    <col width="9" customWidth="1" style="13" min="3" max="3"/>
-    <col width="10" customWidth="1" style="13" min="4" max="4"/>
-    <col width="13" customWidth="1" style="13" min="5" max="5"/>
-    <col width="14" customWidth="1" style="13" min="6" max="6"/>
-    <col width="10" customWidth="1" style="13" min="7" max="8"/>
-    <col width="8.5" customWidth="1" style="13" min="9" max="9"/>
-    <col width="10.1640625" customWidth="1" style="2" min="10" max="10"/>
-    <col width="20" customWidth="1" style="13" min="11" max="13"/>
-    <col width="20" customWidth="1" style="2" min="14" max="14"/>
-    <col width="20" customWidth="1" style="13" min="15" max="18"/>
-    <col width="19" customWidth="1" style="13" min="19" max="19"/>
-    <col width="20" customWidth="1" style="13" min="20" max="21"/>
-    <col width="23.6640625" customWidth="1" style="13" min="24" max="24"/>
-    <col width="76.33203125" customWidth="1" style="4" min="25" max="25"/>
-    <col width="40.83203125" customWidth="1" style="4" min="26" max="26"/>
-  </cols>
+  <dimension ref="A1:AA58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" s="13">
-      <c r="A1" s="11" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
@@ -538,5229 +446,5509 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>legacy_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sampling</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Temperature</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Address mode</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>CoT</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>n_matched</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>jsd</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>recall_minority</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>mcc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>f1_minority</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>precision_minority</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>macro_f1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>cohen_kappa</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>wasserstein</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>tvd</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>pred_mean</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>gt_mean</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>prevalence_error</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ac2_quadratic</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>composite_score</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Source_CSV</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Stage 1 — Configuration screening</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>C0</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H2" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6" t="n">
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1707</v>
       </c>
-      <c r="K2" s="6" t="n">
+      <c r="L2" t="n">
         <v>0.0174335329168782</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" t="n">
         <v>0.0119047619047619</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="N2" t="n">
         <v>0.032250684923876</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" t="n">
         <v>0.0222222222222222</v>
       </c>
-      <c r="O2" s="6" t="n">
+      <c r="P2" t="n">
         <v>0.1666666666666666</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" t="n">
         <v>0.4978740473325311</v>
       </c>
-      <c r="Q2" s="6" t="n">
+      <c r="R2" t="n">
         <v>0.0157644376302238</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" t="n">
         <v>0.0456942003514938</v>
       </c>
-      <c r="S2" s="6" t="n">
+      <c r="T2" t="n">
         <v>0.0456942003514938</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" t="n">
         <v>1.996485061511424</v>
       </c>
-      <c r="U2" s="6" t="n">
+      <c r="V2" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V2" s="6" t="n">
+      <c r="W2" t="n">
         <v>0.0456942003514939</v>
       </c>
-      <c r="W2" s="6" t="n">
+      <c r="X2" t="n">
         <v>-0.0043</v>
       </c>
-      <c r="X2" s="6" t="n">
+      <c r="Y2" t="n">
         <v>5.688872313060457</v>
       </c>
-      <c r="Y2" s="5" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>stages/stage_1_configuration_screening/metrics/all_configs_direct_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z2" s="5" t="n"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Stage 1 — Configuration screening</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H3" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6" t="n">
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1707</v>
       </c>
-      <c r="K3" s="6" t="n">
+      <c r="L3" t="n">
         <v>5.351683532718012e-06</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" t="n">
         <v>0.4047619047619047</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="N3" t="n">
         <v>0.3795011761987824</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" t="n">
         <v>0.4096385542168674</v>
       </c>
-      <c r="O3" s="6" t="n">
+      <c r="P3" t="n">
         <v>0.4146341463414634</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" t="n">
         <v>0.689733070211882</v>
       </c>
-      <c r="Q3" s="6" t="n">
+      <c r="R3" t="n">
         <v>0.3794707440297344</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" t="n">
         <v>0.0011716461628588</v>
       </c>
-      <c r="S3" s="6" t="n">
+      <c r="T3" t="n">
         <v>0.0011716461628588</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" t="n">
         <v>1.951962507322788</v>
       </c>
-      <c r="U3" s="6" t="n">
+      <c r="V3" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V3" s="6" t="n">
+      <c r="W3" t="n">
         <v>0.0011716461628588</v>
       </c>
-      <c r="W3" s="6" t="n">
+      <c r="X3" t="n">
         <v>0.3795</v>
       </c>
-      <c r="X3" s="6" t="n">
+      <c r="Y3" t="n">
         <v>-2.244649259594985</v>
       </c>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>stages/stage_1_configuration_screening/metrics/all_configs_direct_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="n"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Stage 1 — Configuration screening</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6" t="n">
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1707</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="L4" t="n">
         <v>0.0034961729098668</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" t="n">
         <v>0.0714285714285714</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" t="n">
         <v>0.07218018149782</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" t="n">
         <v>0.09677419354838709</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="P4" t="n">
         <v>0.15</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" t="n">
         <v>0.5313658201784488</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="R4" t="n">
         <v>0.0671584987411441</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" t="n">
         <v>0.0257762155828939</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="T4" t="n">
         <v>0.0257762155828939</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" t="n">
         <v>1.976567076742824</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="V4" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V4" s="6" t="n">
+      <c r="W4" t="n">
         <v>0.025776215582894</v>
       </c>
-      <c r="W4" s="6" t="n">
+      <c r="X4" t="n">
         <v>0.06270000000000001</v>
       </c>
-      <c r="X4" s="6" t="n">
+      <c r="Y4" t="n">
         <v>1.91489438752695</v>
       </c>
-      <c r="Y4" s="5" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>stages/stage_1_configuration_screening/metrics/all_configs_direct_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Stage 1 — Configuration screening</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H5" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6" t="n">
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1707</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="L5" t="n">
         <v>0.0007271581029816</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" t="n">
         <v>0.5</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="N5" t="n">
         <v>0.4058293465291389</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" t="n">
         <v>0.4352331606217616</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="P5" t="n">
         <v>0.3853211009174312</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" t="n">
         <v>0.7006963691963202</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="R5" t="n">
         <v>0.4019939641125027</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" t="n">
         <v>0.0146455770357352</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="T5" t="n">
         <v>0.0146455770357352</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" t="n">
         <v>1.936145284124194</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="V5" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="W5" t="n">
         <v>0.0146455770357352</v>
       </c>
-      <c r="W5" s="6" t="n">
+      <c r="X5" t="n">
         <v>0.4014</v>
       </c>
-      <c r="X5" s="6" t="n">
+      <c r="Y5" t="n">
         <v>-1.41868722131077</v>
       </c>
-      <c r="Y5" s="5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>stages/stage_1_configuration_screening/metrics/all_configs_direct_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Stage 1 — Configuration screening</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H6" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6" t="n">
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1707</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="L6" t="n">
         <v>4.607172889229199e-05</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" t="n">
         <v>0.4523809523809524</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="N6" t="n">
         <v>0.4068412011378389</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" t="n">
         <v>0.4367816091954023</v>
       </c>
-      <c r="O6" s="6" t="n">
+      <c r="P6" t="n">
         <v>0.4222222222222222</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" t="n">
         <v>0.7032673478075777</v>
       </c>
-      <c r="Q6" s="6" t="n">
+      <c r="R6" t="n">
         <v>0.4065725900857757</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" t="n">
         <v>0.0035149384885764</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="T6" t="n">
         <v>0.0035149384885764</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" t="n">
         <v>1.947275922671353</v>
       </c>
-      <c r="U6" s="6" t="n">
+      <c r="V6" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V6" s="6" t="n">
+      <c r="W6" t="n">
         <v>0.0035149384885764</v>
       </c>
-      <c r="W6" s="6" t="n">
+      <c r="X6" t="n">
         <v>0.4065</v>
       </c>
-      <c r="X6" s="6" t="n">
+      <c r="Y6" t="n">
         <v>-2.262183561194036</v>
       </c>
-      <c r="Y6" s="5" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>stages/stage_1_configuration_screening/metrics/all_configs_direct_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z6" s="5" t="n"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Stage 1 — Configuration screening</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H7" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6" t="n">
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1707</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="L7" t="n">
         <v>0.000476605853453</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" t="n">
         <v>0.4642857142857143</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="N7" t="n">
         <v>0.3836395953887437</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" t="n">
         <v>0.4148936170212766</v>
       </c>
-      <c r="O7" s="6" t="n">
+      <c r="P7" t="n">
         <v>0.375</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" t="n">
         <v>0.690397831449262</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="R7" t="n">
         <v>0.3812037805987266</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" t="n">
         <v>0.0117164616285881</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="T7" t="n">
         <v>0.0117164616285881</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" t="n">
         <v>1.939074399531342</v>
       </c>
-      <c r="U7" s="6" t="n">
+      <c r="V7" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V7" s="6" t="n">
+      <c r="W7" t="n">
         <v>0.011716461628588</v>
       </c>
-      <c r="W7" s="6" t="n">
+      <c r="X7" t="n">
         <v>0.3808</v>
       </c>
-      <c r="X7" s="6" t="n">
+      <c r="Y7" t="n">
         <v>-1.506223029500218</v>
       </c>
-      <c r="Y7" s="5" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>stages/stage_1_configuration_screening/metrics/all_configs_direct_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z7" s="5" t="n"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Stage 1 — Configuration screening</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>C5</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H8" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6" t="n">
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1707</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="L8" t="n">
         <v>0.0002819908980613</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" t="n">
         <v>0.3809523809523809</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="N8" t="n">
         <v>0.3899858974250385</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" t="n">
         <v>0.4155844155844156</v>
       </c>
-      <c r="O8" s="6" t="n">
+      <c r="P8" t="n">
         <v>0.4571428571428571</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" t="n">
         <v>0.6939885268106127</v>
       </c>
-      <c r="Q8" s="6" t="n">
+      <c r="R8" t="n">
         <v>0.3882158985018995</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" t="n">
         <v>0.008201523140011701</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="T8" t="n">
         <v>0.0082015231400116</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" t="n">
         <v>1.958992384299941</v>
       </c>
-      <c r="U8" s="6" t="n">
+      <c r="V8" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V8" s="6" t="n">
+      <c r="W8" t="n">
         <v>0.0082015231400118</v>
       </c>
-      <c r="W8" s="6" t="n">
+      <c r="X8" t="n">
         <v>0.388</v>
       </c>
-      <c r="X8" s="6" t="n">
+      <c r="Y8" t="n">
         <v>-1.808460560564275</v>
       </c>
-      <c r="Y8" s="5" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>stages/stage_1_configuration_screening/metrics/all_configs_direct_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z8" s="5" t="n"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Stage 1 — Configuration screening</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H9" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6" t="n">
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1707</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="L9" t="n">
         <v>0.0002747896280029</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" t="n">
         <v>0.4761904761904761</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="N9" t="n">
         <v>0.4070343610236951</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" t="n">
         <v>0.4371584699453552</v>
       </c>
-      <c r="O9" s="6" t="n">
+      <c r="P9" t="n">
         <v>0.404040404040404</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" t="n">
         <v>0.7026398973063204</v>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="R9" t="n">
         <v>0.4055060203077609</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" t="n">
         <v>0.0087873462214411</v>
       </c>
-      <c r="S9" s="6" t="n">
+      <c r="T9" t="n">
         <v>0.0087873462214411</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" t="n">
         <v>1.942003514938489</v>
       </c>
-      <c r="U9" s="6" t="n">
+      <c r="V9" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V9" s="6" t="n">
+      <c r="W9" t="n">
         <v>0.0087873462214409</v>
       </c>
-      <c r="W9" s="6" t="n">
+      <c r="X9" t="n">
         <v>0.4053</v>
       </c>
-      <c r="X9" s="6" t="n">
+      <c r="Y9" t="n">
         <v>-1.881889971457342</v>
       </c>
-      <c r="Y9" s="5" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>stages/stage_1_configuration_screening/metrics/all_configs_direct_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z9" s="5" t="n"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Stage 1 — Configuration screening</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H10" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6" t="n">
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1707</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="L10" t="n">
         <v>0.000899539880171</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" t="n">
         <v>0.5119047619047619</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="N10" t="n">
         <v>0.4100569833846915</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" t="n">
         <v>0.4387755102040816</v>
       </c>
-      <c r="O10" s="6" t="n">
+      <c r="P10" t="n">
         <v>0.3839285714285714</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" t="n">
         <v>0.7022963940081937</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="R10" t="n">
         <v>0.4053319651883099</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" t="n">
         <v>0.0164030462800234</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="T10" t="n">
         <v>0.0164030462800234</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" t="n">
         <v>1.934387814879906</v>
       </c>
-      <c r="U10" s="6" t="n">
+      <c r="V10" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V10" s="6" t="n">
+      <c r="W10" t="n">
         <v>0.0164030462800233</v>
       </c>
-      <c r="W10" s="6" t="n">
+      <c r="X10" t="n">
         <v>0.4046</v>
       </c>
-      <c r="X10" s="6" t="n">
+      <c r="Y10" t="n">
         <v>-1.30369561117835</v>
       </c>
-      <c r="Y10" s="5" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>stages/stage_1_configuration_screening/metrics/all_configs_direct_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z10" s="5" t="n"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Stage 1 — Configuration screening</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H11" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6" t="n">
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>1707</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="L11" t="n">
         <v>0.0151037251175372</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" t="n">
         <v>0.0357142857142857</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" t="n">
         <v>0.095630240376987</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" t="n">
         <v>0.06451612903225799</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="P11" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" t="n">
         <v>0.5191596001981525</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="R11" t="n">
         <v>0.0555205769560985</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" t="n">
         <v>0.0439367311072056</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="T11" t="n">
         <v>0.0439367311072056</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" t="n">
         <v>1.994727592267135</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="V11" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="W11" t="n">
         <v>0.0439367311072056</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="X11" t="n">
         <v>0.0383</v>
       </c>
-      <c r="X11" s="6" t="n">
+      <c r="Y11" t="n">
         <v>4.792918181999762</v>
       </c>
-      <c r="Y11" s="5" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>stages/stage_1_configuration_screening/metrics/all_configs_direct_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z11" s="5" t="n"/>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Stage 1 — Configuration screening</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>C9</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H12" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="6" t="n">
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1707</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="L12" t="n">
         <v>0.0025168058445927</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" t="n">
         <v>0.5119047619047619</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="N12" t="n">
         <v>0.3683542920720132</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" t="n">
         <v>0.3963133640552995</v>
       </c>
-      <c r="O12" s="6" t="n">
+      <c r="P12" t="n">
         <v>0.3233082706766917</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" t="n">
         <v>0.6776687245675309</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="R12" t="n">
         <v>0.357560870502047</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" t="n">
         <v>0.028705330990041</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="T12" t="n">
         <v>0.028705330990041</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" t="n">
         <v>1.922085530169889</v>
       </c>
-      <c r="U12" s="6" t="n">
+      <c r="V12" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V12" s="6" t="n">
+      <c r="W12" t="n">
         <v>0.0287053309900409</v>
       </c>
-      <c r="W12" s="6" t="n">
+      <c r="X12" t="n">
         <v>0.3553</v>
       </c>
-      <c r="X12" s="6" t="n">
+      <c r="Y12" t="n">
         <v>0.029104332212813</v>
       </c>
-      <c r="Y12" s="5" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>stages/stage_1_configuration_screening/metrics/all_configs_direct_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z12" s="5" t="n"/>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H13" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8" t="n">
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>1707</v>
       </c>
-      <c r="K13" s="8" t="n">
+      <c r="L13" t="n">
         <v>0.01765219950239729</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="M13" t="n">
         <v>0.3095238095238095</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="N13" t="n">
         <v>0.1122983078932431</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="O13" t="n">
         <v>0.161993769470405</v>
       </c>
-      <c r="O13" s="8" t="n">
+      <c r="P13" t="n">
         <v>0.109704641350211</v>
       </c>
-      <c r="P13" s="8" t="n">
+      <c r="Q13" t="n">
         <v>0.5375115953721246</v>
       </c>
-      <c r="Q13" s="8" t="n">
+      <c r="R13" t="n">
         <v>0.09632948983628231</v>
       </c>
-      <c r="R13" s="8" t="n">
+      <c r="S13" t="n">
         <v>0.08963093145869946</v>
       </c>
-      <c r="S13" s="8" t="n">
+      <c r="T13" t="n">
         <v>0.08963093145869948</v>
       </c>
-      <c r="T13" s="8" t="n">
+      <c r="U13" t="n">
         <v>1.86115992970123</v>
       </c>
-      <c r="U13" s="8" t="n">
+      <c r="V13" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="W13" t="n">
         <v>0.08963093145869938</v>
       </c>
-      <c r="W13" s="8" t="n">
+      <c r="X13" t="n">
         <v>0.1387</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="Y13" t="n">
         <v>-0.5076280216273126</v>
       </c>
-      <c r="Y13" s="7" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z13" s="7" t="n"/>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="8" t="n">
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>1707</v>
       </c>
-      <c r="K14" s="8" t="n">
+      <c r="L14" t="n">
         <v>0.01564269168410411</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="M14" t="n">
         <v>0.3928571428571428</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="N14" t="n">
         <v>0.1748336682994243</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="O14" t="n">
         <v>0.2129032258064516</v>
       </c>
-      <c r="O14" s="8" t="n">
+      <c r="P14" t="n">
         <v>0.1460176991150443</v>
       </c>
-      <c r="P14" s="8" t="n">
+      <c r="Q14" t="n">
         <v>0.5671474891918855</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="R14" t="n">
         <v>0.1520637130956308</v>
       </c>
-      <c r="R14" s="8" t="n">
+      <c r="S14" t="n">
         <v>0.08318687756297596</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="T14" t="n">
         <v>0.08318687756297601</v>
       </c>
-      <c r="T14" s="8" t="n">
+      <c r="U14" t="n">
         <v>1.867603983596954</v>
       </c>
-      <c r="U14" s="8" t="n">
+      <c r="V14" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V14" s="8" t="n">
+      <c r="W14" t="n">
         <v>0.08318687756297583</v>
       </c>
-      <c r="W14" s="8" t="n">
+      <c r="X14" t="n">
         <v>0.1492</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="Y14" t="n">
         <v>-1.833169956226254</v>
       </c>
-      <c r="Y14" s="7" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z14" s="7" t="n"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H15" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="8" t="n">
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>1707</v>
       </c>
-      <c r="K15" s="8" t="n">
+      <c r="L15" t="n">
         <v>0.01672925369559385</v>
       </c>
-      <c r="L15" s="8" t="n">
+      <c r="M15" t="n">
         <v>0.3095238095238095</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="N15" t="n">
         <v>0.1152539396888841</v>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="O15" t="n">
         <v>0.1645569620253164</v>
       </c>
-      <c r="O15" s="8" t="n">
+      <c r="P15" t="n">
         <v>0.1120689655172414</v>
       </c>
-      <c r="P15" s="8" t="n">
+      <c r="Q15" t="n">
         <v>0.5396703467324775</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="R15" t="n">
         <v>0.09948924537803028</v>
       </c>
-      <c r="R15" s="8" t="n">
+      <c r="S15" t="n">
         <v>0.08670181605155242</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="T15" t="n">
         <v>0.08670181605155244</v>
       </c>
-      <c r="T15" s="8" t="n">
+      <c r="U15" t="n">
         <v>1.864089045108377</v>
       </c>
-      <c r="U15" s="8" t="n">
+      <c r="V15" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V15" s="8" t="n">
+      <c r="W15" t="n">
         <v>0.08670181605155225</v>
       </c>
-      <c r="W15" s="8" t="n">
+      <c r="X15" t="n">
         <v>0.145</v>
       </c>
-      <c r="X15" s="8" t="n">
+      <c r="Y15" t="n">
         <v>-1.562680750459088</v>
       </c>
-      <c r="Y15" s="7" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z15" s="7" t="n"/>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H16" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="8" t="n">
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>1707</v>
       </c>
-      <c r="K16" s="8" t="n">
+      <c r="L16" t="n">
         <v>0.02169266532091244</v>
       </c>
-      <c r="L16" s="8" t="n">
+      <c r="M16" t="n">
         <v>0.5</v>
       </c>
-      <c r="M16" s="8" t="n">
+      <c r="N16" t="n">
         <v>0.2215736455596469</v>
       </c>
-      <c r="N16" s="8" t="n">
+      <c r="O16" t="n">
         <v>0.2456140350877193</v>
       </c>
-      <c r="O16" s="8" t="n">
+      <c r="P16" t="n">
         <v>0.1627906976744186</v>
       </c>
-      <c r="P16" s="8" t="n">
+      <c r="Q16" t="n">
         <v>0.5808148300438596</v>
       </c>
-      <c r="Q16" s="8" t="n">
+      <c r="R16" t="n">
         <v>0.18511240632806</v>
       </c>
-      <c r="R16" s="8" t="n">
+      <c r="S16" t="n">
         <v>0.101933216168717</v>
       </c>
-      <c r="S16" s="8" t="n">
+      <c r="T16" t="n">
         <v>0.1019332161687171</v>
       </c>
-      <c r="T16" s="8" t="n">
+      <c r="U16" t="n">
         <v>1.848857644991213</v>
       </c>
-      <c r="U16" s="8" t="n">
+      <c r="V16" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V16" s="8" t="n">
+      <c r="W16" t="n">
         <v>0.101933216168717</v>
       </c>
-      <c r="W16" s="8" t="n">
+      <c r="X16" t="n">
         <v>0.1311</v>
       </c>
-      <c r="X16" s="8" t="n">
+      <c r="Y16" t="n">
         <v>3.903478728312663</v>
       </c>
-      <c r="Y16" s="7" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z16" s="7" t="n"/>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="G17" t="n">
         <v>0.8</v>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H17" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="8" t="n">
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>1707</v>
       </c>
-      <c r="K17" s="8" t="n">
+      <c r="L17" t="n">
         <v>0.02431856772872211</v>
       </c>
-      <c r="L17" s="8" t="n">
+      <c r="M17" t="n">
         <v>0.3571428571428572</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="N17" t="n">
         <v>0.1234981458616602</v>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="O17" t="n">
         <v>0.1690140845070423</v>
       </c>
-      <c r="O17" s="8" t="n">
+      <c r="P17" t="n">
         <v>0.1107011070110701</v>
       </c>
-      <c r="P17" s="8" t="n">
+      <c r="Q17" t="n">
         <v>0.5362886702365222</v>
       </c>
-      <c r="Q17" s="8" t="n">
+      <c r="R17" t="n">
         <v>0.1015100177176839</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="S17" t="n">
         <v>0.1095489162272993</v>
       </c>
-      <c r="S17" s="8" t="n">
+      <c r="T17" t="n">
         <v>0.1095489162272993</v>
       </c>
-      <c r="T17" s="8" t="n">
+      <c r="U17" t="n">
         <v>1.84124194493263</v>
       </c>
-      <c r="U17" s="8" t="n">
+      <c r="V17" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V17" s="8" t="n">
+      <c r="W17" t="n">
         <v>0.1095489162272993</v>
       </c>
-      <c r="W17" s="8" t="n">
+      <c r="X17" t="n">
         <v>0.1239</v>
       </c>
-      <c r="X17" s="8" t="n">
+      <c r="Y17" t="n">
         <v>-2.283012904951979</v>
       </c>
-      <c r="Y17" s="7" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z17" s="7" t="n"/>
+      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="G18" t="n">
         <v>0.8</v>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H18" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="8" t="n">
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1707</v>
       </c>
-      <c r="K18" s="8" t="n">
+      <c r="L18" t="n">
         <v>0.02576960440970211</v>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="M18" t="n">
         <v>0.3690476190476191</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="N18" t="n">
         <v>0.1270399950135578</v>
       </c>
-      <c r="N18" s="8" t="n">
+      <c r="O18" t="n">
         <v>0.1712707182320442</v>
       </c>
-      <c r="O18" s="8" t="n">
+      <c r="P18" t="n">
         <v>0.1115107913669065</v>
       </c>
-      <c r="P18" s="8" t="n">
+      <c r="Q18" t="n">
         <v>0.5364872595092069</v>
       </c>
-      <c r="Q18" s="8" t="n">
+      <c r="R18" t="n">
         <v>0.1035134709311486</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="S18" t="n">
         <v>0.1136496777973052</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="T18" t="n">
         <v>0.1136496777973052</v>
       </c>
-      <c r="T18" s="8" t="n">
+      <c r="U18" t="n">
         <v>1.837141183362625</v>
       </c>
-      <c r="U18" s="8" t="n">
+      <c r="V18" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V18" s="8" t="n">
+      <c r="W18" t="n">
         <v>0.1136496777973051</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="X18" t="n">
         <v>0.1026</v>
       </c>
-      <c r="X18" s="8" t="n">
+      <c r="Y18" t="n">
         <v>-1.041315550892445</v>
       </c>
-      <c r="Y18" s="7" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z18" s="7" t="n"/>
+      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="G19" t="n">
         <v>0.8</v>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H19" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="8" t="n">
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1707</v>
       </c>
-      <c r="K19" s="8" t="n">
+      <c r="L19" t="n">
         <v>0.02810003492479322</v>
       </c>
-      <c r="L19" s="8" t="n">
+      <c r="M19" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="N19" t="n">
         <v>0.09950648323807915</v>
       </c>
-      <c r="N19" s="8" t="n">
+      <c r="O19" t="n">
         <v>0.1501340482573726</v>
       </c>
-      <c r="O19" s="8" t="n">
+      <c r="P19" t="n">
         <v>0.09688581314878893</v>
       </c>
-      <c r="P19" s="8" t="n">
+      <c r="Q19" t="n">
         <v>0.5229460113039577</v>
       </c>
-      <c r="Q19" s="8" t="n">
+      <c r="R19" t="n">
         <v>0.07997837319500345</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="S19" t="n">
         <v>0.1200937316930287</v>
       </c>
-      <c r="S19" s="8" t="n">
+      <c r="T19" t="n">
         <v>0.1200937316930287</v>
       </c>
-      <c r="T19" s="8" t="n">
+      <c r="U19" t="n">
         <v>1.830697129466901</v>
       </c>
-      <c r="U19" s="8" t="n">
+      <c r="V19" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V19" s="8" t="n">
+      <c r="W19" t="n">
         <v>0.1200937316930286</v>
       </c>
-      <c r="W19" s="8" t="n">
+      <c r="X19" t="n">
         <v>0.1008</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="Y19" t="n">
         <v>-0.656033559665588</v>
       </c>
-      <c r="Y19" s="7" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z19" s="7" t="n"/>
+      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="G20" t="n">
         <v>0.8</v>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H20" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="8" t="n">
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1707</v>
       </c>
-      <c r="K20" s="8" t="n">
+      <c r="L20" t="n">
         <v>0.03181703305079935</v>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="M20" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="N20" t="n">
         <v>0.091381093509374</v>
       </c>
-      <c r="N20" s="8" t="n">
+      <c r="O20" t="n">
         <v>0.1435897435897436</v>
       </c>
-      <c r="O20" s="8" t="n">
+      <c r="P20" t="n">
         <v>0.0915032679738562</v>
       </c>
-      <c r="P20" s="8" t="n">
+      <c r="Q20" t="n">
         <v>0.5165700040700041</v>
       </c>
-      <c r="Q20" s="8" t="n">
+      <c r="R20" t="n">
         <v>0.07192319337415887</v>
       </c>
-      <c r="R20" s="8" t="n">
+      <c r="S20" t="n">
         <v>0.1300527240773287</v>
       </c>
-      <c r="S20" s="8" t="n">
+      <c r="T20" t="n">
         <v>0.1300527240773287</v>
       </c>
-      <c r="T20" s="8" t="n">
+      <c r="U20" t="n">
         <v>1.820738137082601</v>
       </c>
-      <c r="U20" s="8" t="n">
+      <c r="V20" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V20" s="8" t="n">
+      <c r="W20" t="n">
         <v>0.1300527240773286</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="X20" t="n">
         <v>0.08019999999999999</v>
       </c>
-      <c r="X20" s="8" t="n">
+      <c r="Y20" t="n">
         <v>3.980362015510012</v>
       </c>
-      <c r="Y20" s="7" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z20" s="7" t="n"/>
+      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="G21" t="n">
         <v>0.4</v>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H21" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="8" t="n">
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1707</v>
       </c>
-      <c r="K21" s="8" t="n">
+      <c r="L21" t="n">
         <v>0.02289326594757894</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="M21" t="n">
         <v>0.3452380952380952</v>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="N21" t="n">
         <v>0.1199106963031641</v>
       </c>
-      <c r="N21" s="8" t="n">
+      <c r="O21" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="O21" s="8" t="n">
+      <c r="P21" t="n">
         <v>0.1098484848484848</v>
       </c>
-      <c r="P21" s="8" t="n">
+      <c r="Q21" t="n">
         <v>0.5360404435746902</v>
       </c>
-      <c r="Q21" s="8" t="n">
+      <c r="R21" t="n">
         <v>0.09942803501648223</v>
       </c>
-      <c r="R21" s="8" t="n">
+      <c r="S21" t="n">
         <v>0.1054481546572935</v>
       </c>
-      <c r="S21" s="8" t="n">
+      <c r="T21" t="n">
         <v>0.1054481546572935</v>
       </c>
-      <c r="T21" s="8" t="n">
+      <c r="U21" t="n">
         <v>1.845342706502636</v>
       </c>
-      <c r="U21" s="8" t="n">
+      <c r="V21" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V21" s="8" t="n">
+      <c r="W21" t="n">
         <v>0.1054481546572934</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="X21" t="n">
         <v>0.1163</v>
       </c>
-      <c r="X21" s="8" t="n">
+      <c r="Y21" t="n">
         <v>-2.913491484483405</v>
       </c>
-      <c r="Y21" s="7" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z21" s="7" t="n"/>
+      <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="G22" t="n">
         <v>0.4</v>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H22" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="8" t="n">
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1707</v>
       </c>
-      <c r="K22" s="8" t="n">
+      <c r="L22" t="n">
         <v>0.02229049611733434</v>
       </c>
-      <c r="L22" s="8" t="n">
+      <c r="M22" t="n">
         <v>0.3452380952380952</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="N22" t="n">
         <v>0.1215836597339032</v>
       </c>
-      <c r="N22" s="8" t="n">
+      <c r="O22" t="n">
         <v>0.1681159420289855</v>
       </c>
-      <c r="O22" s="8" t="n">
+      <c r="P22" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="P22" s="8" t="n">
+      <c r="Q22" t="n">
         <v>0.5373000694178816</v>
       </c>
-      <c r="Q22" s="8" t="n">
+      <c r="R22" t="n">
         <v>0.1011948989757223</v>
       </c>
-      <c r="R22" s="8" t="n">
+      <c r="S22" t="n">
         <v>0.1036906854130053</v>
       </c>
-      <c r="S22" s="8" t="n">
+      <c r="T22" t="n">
         <v>0.1036906854130053</v>
       </c>
-      <c r="T22" s="8" t="n">
+      <c r="U22" t="n">
         <v>1.847100175746925</v>
       </c>
-      <c r="U22" s="8" t="n">
+      <c r="V22" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="W22" t="n">
         <v>0.1036906854130051</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="X22" t="n">
         <v>0.0998</v>
       </c>
-      <c r="X22" s="8" t="n">
+      <c r="Y22" t="n">
         <v>-0.9858721683788824</v>
       </c>
-      <c r="Y22" s="7" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z22" s="7" t="n"/>
+      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="G23" t="n">
         <v>0.4</v>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H23" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="8" t="n">
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1707</v>
       </c>
-      <c r="K23" s="8" t="n">
+      <c r="L23" t="n">
         <v>0.02309527526516076</v>
       </c>
-      <c r="L23" s="8" t="n">
+      <c r="M23" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="M23" s="8" t="n">
+      <c r="N23" t="n">
         <v>0.111878954576169</v>
       </c>
-      <c r="N23" s="8" t="n">
+      <c r="O23" t="n">
         <v>0.160458452722063</v>
       </c>
-      <c r="O23" s="8" t="n">
+      <c r="P23" t="n">
         <v>0.1056603773584906</v>
       </c>
-      <c r="P23" s="8" t="n">
+      <c r="Q23" t="n">
         <v>0.53243151021095</v>
       </c>
-      <c r="Q23" s="8" t="n">
+      <c r="R23" t="n">
         <v>0.09265215711245733</v>
       </c>
-      <c r="R23" s="8" t="n">
+      <c r="S23" t="n">
         <v>0.1060339777387229</v>
       </c>
-      <c r="S23" s="8" t="n">
+      <c r="T23" t="n">
         <v>0.1060339777387229</v>
       </c>
-      <c r="T23" s="8" t="n">
+      <c r="U23" t="n">
         <v>1.844756883421207</v>
       </c>
-      <c r="U23" s="8" t="n">
+      <c r="V23" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V23" s="8" t="n">
+      <c r="W23" t="n">
         <v>0.1060339777387229</v>
       </c>
-      <c r="W23" s="8" t="n">
+      <c r="X23" t="n">
         <v>0.1017</v>
       </c>
-      <c r="X23" s="8" t="n">
+      <c r="Y23" t="n">
         <v>-0.0628186447443011</v>
       </c>
-      <c r="Y23" s="7" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z23" s="7" t="n"/>
+      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="G24" t="n">
         <v>0.4</v>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H24" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="8" t="n">
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1707</v>
       </c>
-      <c r="K24" s="8" t="n">
+      <c r="L24" t="n">
         <v>0.0291790098481546</v>
       </c>
-      <c r="L24" s="8" t="n">
+      <c r="M24" t="n">
         <v>0.4047619047619048</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="N24" t="n">
         <v>0.140103181701047</v>
       </c>
-      <c r="N24" s="8" t="n">
+      <c r="O24" t="n">
         <v>0.1798941798941799</v>
       </c>
-      <c r="O24" s="8" t="n">
+      <c r="P24" t="n">
         <v>0.1156462585034014</v>
       </c>
-      <c r="P24" s="8" t="n">
+      <c r="Q24" t="n">
         <v>0.5388930715017671</v>
       </c>
-      <c r="Q24" s="8" t="n">
+      <c r="R24" t="n">
         <v>0.1119133210484448</v>
       </c>
-      <c r="R24" s="8" t="n">
+      <c r="S24" t="n">
         <v>0.1230228471001757</v>
       </c>
-      <c r="S24" s="8" t="n">
+      <c r="T24" t="n">
         <v>0.1230228471001757</v>
       </c>
-      <c r="T24" s="8" t="n">
+      <c r="U24" t="n">
         <v>1.827768014059754</v>
       </c>
-      <c r="U24" s="8" t="n">
+      <c r="V24" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V24" s="8" t="n">
+      <c r="W24" t="n">
         <v>0.1230228471001757</v>
       </c>
-      <c r="W24" s="8" t="n">
+      <c r="X24" t="n">
         <v>0.07580000000000001</v>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="Y24" t="n">
         <v>3.962182297606596</v>
       </c>
-      <c r="Y24" s="7" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z24" s="7" t="n"/>
+      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Phase 5</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="G25" t="n">
         <v>0.4</v>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H25" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="8" t="n">
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1707</v>
       </c>
-      <c r="K25" s="8" t="n">
+      <c r="L25" t="n">
         <v>3.403649742297507e-05</v>
       </c>
-      <c r="L25" s="8" t="n">
+      <c r="M25" t="n">
         <v>0.4047619047619047</v>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="N25" t="n">
         <v>0.3881864469112423</v>
       </c>
-      <c r="N25" s="8" t="n">
+      <c r="O25" t="n">
         <v>0.4171779141104294</v>
       </c>
-      <c r="O25" s="8" t="n">
+      <c r="P25" t="n">
         <v>0.430379746835443</v>
       </c>
-      <c r="P25" s="8" t="n">
+      <c r="Q25" t="n">
         <v>0.6939780680979708</v>
       </c>
-      <c r="Q25" s="8" t="n">
+      <c r="R25" t="n">
         <v>0.387985009567157</v>
       </c>
-      <c r="R25" s="8" t="n">
+      <c r="S25" t="n">
         <v>0.002929115407147</v>
       </c>
-      <c r="S25" s="8" t="n">
+      <c r="T25" t="n">
         <v>0.002929115407147</v>
       </c>
-      <c r="T25" s="8" t="n">
+      <c r="U25" t="n">
         <v>1.953719976567077</v>
       </c>
-      <c r="U25" s="8" t="n">
+      <c r="V25" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V25" s="8" t="n">
+      <c r="W25" t="n">
         <v>0.0029291154071471</v>
       </c>
-      <c r="W25" s="8" t="n">
+      <c r="X25" t="n">
         <v>0.388</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="Y25" t="n">
         <v>-0.8987764634474207</v>
       </c>
-      <c r="Y25" s="7" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_direct_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z25" s="7" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>Phase 5 pacdemons-only originally; Phase 11 added womenwork/neilang</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Phase 5</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="G26" t="n">
         <v>0.8</v>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H26" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="8" t="n">
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1707</v>
       </c>
-      <c r="K26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="8" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>0.4404761904761904</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="N26" t="n">
         <v>0.4115174720535164</v>
       </c>
-      <c r="N26" s="8" t="n">
+      <c r="O26" t="n">
         <v>0.4404761904761904</v>
       </c>
-      <c r="O26" s="8" t="n">
+      <c r="P26" t="n">
         <v>0.4404761904761904</v>
       </c>
-      <c r="P26" s="8" t="n">
+      <c r="Q26" t="n">
         <v>0.7057587360267582</v>
       </c>
-      <c r="Q26" s="8" t="n">
+      <c r="R26" t="n">
         <v>0.4115174720535164</v>
       </c>
-      <c r="R26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="8" t="n">
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="U26" s="8" t="n">
+      <c r="V26" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="8" t="n">
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
         <v>0.4115</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="Y26" t="n">
         <v>-1.981163137981051</v>
       </c>
-      <c r="Y26" s="7" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z26" s="7" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>Phase 5 pacdemons-only originally; Phase 11 added womenwork/neilang</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Phase 5</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="G27" t="n">
         <v>0.4</v>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H27" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="8" t="n">
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1707</v>
       </c>
-      <c r="K27" s="8" t="n">
+      <c r="L27" t="n">
         <v>5.232199427603889e-06</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="M27" t="n">
         <v>0.4404761904761904</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="N27" t="n">
         <v>0.405736432634551</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="O27" t="n">
         <v>0.4352941176470588</v>
       </c>
-      <c r="O27" s="8" t="n">
+      <c r="P27" t="n">
         <v>0.4302325581395348</v>
       </c>
-      <c r="P27" s="8" t="n">
+      <c r="Q27" t="n">
         <v>0.702850511351273</v>
       </c>
-      <c r="Q27" s="8" t="n">
+      <c r="R27" t="n">
         <v>0.4057053332462954</v>
       </c>
-      <c r="R27" s="8" t="n">
+      <c r="S27" t="n">
         <v>0.0011716461628588</v>
       </c>
-      <c r="S27" s="8" t="n">
+      <c r="T27" t="n">
         <v>0.0011716461628588</v>
       </c>
-      <c r="T27" s="8" t="n">
+      <c r="U27" t="n">
         <v>1.949619214997071</v>
       </c>
-      <c r="U27" s="8" t="n">
+      <c r="V27" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V27" s="8" t="n">
+      <c r="W27" t="n">
         <v>0.0011716461628588</v>
       </c>
-      <c r="W27" s="8" t="n">
+      <c r="X27" t="n">
         <v>0.4057</v>
       </c>
-      <c r="X27" s="8" t="n">
+      <c r="Y27" t="n">
         <v>-2.120300437553805</v>
       </c>
-      <c r="Y27" s="7" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_direct_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z27" s="7" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>Phase 5 pacdemons-only originally; Phase 11 added womenwork/neilang</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Phase 5</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="G28" t="n">
         <v>0.8</v>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H28" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="8" t="n">
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1707</v>
       </c>
-      <c r="K28" s="8" t="n">
+      <c r="L28" t="n">
         <v>3.216746520577309e-05</v>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="M28" t="n">
         <v>0.4404761904761904</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="N28" t="n">
         <v>0.3974106126599782</v>
       </c>
-      <c r="N28" s="8" t="n">
+      <c r="O28" t="n">
         <v>0.4277456647398844</v>
       </c>
-      <c r="O28" s="8" t="n">
+      <c r="P28" t="n">
         <v>0.4157303370786517</v>
       </c>
-      <c r="P28" s="8" t="n">
+      <c r="Q28" t="n">
         <v>0.698599768500766</v>
       </c>
-      <c r="Q28" s="8" t="n">
+      <c r="R28" t="n">
         <v>0.3972264132772624</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="S28" t="n">
         <v>0.002929115407147</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="T28" t="n">
         <v>0.002929115407147</v>
       </c>
-      <c r="T28" s="8" t="n">
+      <c r="U28" t="n">
         <v>1.947861745752783</v>
       </c>
-      <c r="U28" s="8" t="n">
+      <c r="V28" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V28" s="8" t="n">
+      <c r="W28" t="n">
         <v>0.0029291154071469</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="X28" t="n">
         <v>0.3972</v>
       </c>
-      <c r="X28" s="8" t="n">
+      <c r="Y28" t="n">
         <v>-0.7052151777963744</v>
       </c>
-      <c r="Y28" s="7" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z28" s="7" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>Phase 5 pacdemons-only originally; Phase 11 added womenwork/neilang</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Phase 5</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="G29" t="n">
         <v>0.4</v>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H29" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="8" t="n">
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1707</v>
       </c>
-      <c r="K29" s="8" t="n">
+      <c r="L29" t="n">
         <v>0.0003898397230844</v>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="M29" t="n">
         <v>0.4523809523809524</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="N29" t="n">
         <v>0.3768395352497808</v>
       </c>
-      <c r="N29" s="8" t="n">
+      <c r="O29" t="n">
         <v>0.4086021505376344</v>
       </c>
-      <c r="O29" s="8" t="n">
+      <c r="P29" t="n">
         <v>0.3725490196078431</v>
       </c>
-      <c r="P29" s="8" t="n">
+      <c r="Q29" t="n">
         <v>0.6872626613902546</v>
       </c>
-      <c r="Q29" s="8" t="n">
+      <c r="R29" t="n">
         <v>0.3748626675455944</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="S29" t="n">
         <v>0.0105448154657293</v>
       </c>
-      <c r="S29" s="8" t="n">
+      <c r="T29" t="n">
         <v>0.0105448154657293</v>
       </c>
-      <c r="T29" s="8" t="n">
+      <c r="U29" t="n">
         <v>1.9402460456942</v>
       </c>
-      <c r="U29" s="8" t="n">
+      <c r="V29" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V29" s="8" t="n">
+      <c r="W29" t="n">
         <v>0.0105448154657292</v>
       </c>
-      <c r="W29" s="8" t="n">
+      <c r="X29" t="n">
         <v>0.3745</v>
       </c>
-      <c r="X29" s="8" t="n">
+      <c r="Y29" t="n">
         <v>1.61887156996597</v>
       </c>
-      <c r="Y29" s="7" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_direct_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z29" s="7" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>Phase 5 pacdemons-only originally; Phase 11 added womenwork/neilang</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Phase 5</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="G30" t="n">
         <v>0.8</v>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H30" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="8" t="n">
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>1707</v>
       </c>
-      <c r="K30" s="8" t="n">
+      <c r="L30" t="n">
         <v>0.0003494478566051</v>
       </c>
-      <c r="L30" s="8" t="n">
+      <c r="M30" t="n">
         <v>0.4642857142857143</v>
       </c>
-      <c r="M30" s="8" t="n">
+      <c r="N30" t="n">
         <v>0.3906263538343942</v>
       </c>
-      <c r="N30" s="8" t="n">
+      <c r="O30" t="n">
         <v>0.4216216216216216</v>
       </c>
-      <c r="O30" s="8" t="n">
+      <c r="P30" t="n">
         <v>0.3861386138613861</v>
       </c>
-      <c r="P30" s="8" t="n">
+      <c r="Q30" t="n">
         <v>0.6942422137219288</v>
       </c>
-      <c r="Q30" s="8" t="n">
+      <c r="R30" t="n">
         <v>0.3887801303095102</v>
       </c>
-      <c r="R30" s="8" t="n">
+      <c r="S30" t="n">
         <v>0.009958992384299901</v>
       </c>
-      <c r="S30" s="8" t="n">
+      <c r="T30" t="n">
         <v>0.009958992384299901</v>
       </c>
-      <c r="T30" s="8" t="n">
+      <c r="U30" t="n">
         <v>1.94083186877563</v>
       </c>
-      <c r="U30" s="8" t="n">
+      <c r="V30" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V30" s="8" t="n">
+      <c r="W30" t="n">
         <v>0.0099589923842997</v>
       </c>
-      <c r="W30" s="8" t="n">
+      <c r="X30" t="n">
         <v>0.3885</v>
       </c>
-      <c r="X30" s="8" t="n">
+      <c r="Y30" t="n">
         <v>1.325616956840049</v>
       </c>
-      <c r="Y30" s="7" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z30" s="7" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>Phase 5 pacdemons-only originally; Phase 11 added womenwork/neilang</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Phase 5</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="G31" t="n">
         <v>0.4</v>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H31" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="8" t="n">
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>1707</v>
       </c>
-      <c r="K31" s="8" t="n">
+      <c r="L31" t="n">
         <v>0.000899539880171</v>
       </c>
-      <c r="L31" s="8" t="n">
+      <c r="M31" t="n">
         <v>0.5238095238095238</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="N31" t="n">
         <v>0.420995168352386</v>
       </c>
-      <c r="N31" s="8" t="n">
+      <c r="O31" t="n">
         <v>0.4489795918367347</v>
       </c>
-      <c r="O31" s="8" t="n">
+      <c r="P31" t="n">
         <v>0.3928571428571428</v>
       </c>
-      <c r="P31" s="8" t="n">
+      <c r="Q31" t="n">
         <v>0.7077091868444083</v>
       </c>
-      <c r="Q31" s="8" t="n">
+      <c r="R31" t="n">
         <v>0.4161441112757953</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="S31" t="n">
         <v>0.0164030462800234</v>
       </c>
-      <c r="S31" s="8" t="n">
+      <c r="T31" t="n">
         <v>0.0164030462800234</v>
       </c>
-      <c r="T31" s="8" t="n">
+      <c r="U31" t="n">
         <v>1.934387814879906</v>
       </c>
-      <c r="U31" s="8" t="n">
+      <c r="V31" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V31" s="8" t="n">
+      <c r="W31" t="n">
         <v>0.0164030462800233</v>
       </c>
-      <c r="W31" s="8" t="n">
+      <c r="X31" t="n">
         <v>0.4154</v>
       </c>
-      <c r="X31" s="8" t="n">
+      <c r="Y31" t="n">
         <v>1.400205331035257</v>
       </c>
-      <c r="Y31" s="7" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_direct_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z31" s="7" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>Phase 5 pacdemons-only originally; Phase 11 added womenwork/neilang</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Phase 5</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="G32" t="n">
         <v>0.8</v>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H32" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="8" t="n">
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>1707</v>
       </c>
-      <c r="K32" s="8" t="n">
+      <c r="L32" t="n">
         <v>0.0009605324299166999</v>
       </c>
-      <c r="L32" s="8" t="n">
+      <c r="M32" t="n">
         <v>0.5357142857142857</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="N32" t="n">
         <v>0.4296167221484333</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="O32" t="n">
         <v>0.4568527918781725</v>
       </c>
-      <c r="O32" s="8" t="n">
+      <c r="P32" t="n">
         <v>0.3982300884955752</v>
       </c>
-      <c r="P32" s="8" t="n">
+      <c r="Q32" t="n">
         <v>0.7117959949443707</v>
       </c>
-      <c r="Q32" s="8" t="n">
+      <c r="R32" t="n">
         <v>0.4243558833262422</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="S32" t="n">
         <v>0.0169888693614528</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="T32" t="n">
         <v>0.0169888693614528</v>
       </c>
-      <c r="T32" s="8" t="n">
+      <c r="U32" t="n">
         <v>1.933801991798477</v>
       </c>
-      <c r="U32" s="8" t="n">
+      <c r="V32" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V32" s="8" t="n">
+      <c r="W32" t="n">
         <v>0.0169888693614528</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="X32" t="n">
         <v>0.4236</v>
       </c>
-      <c r="X32" s="8" t="n">
+      <c r="Y32" t="n">
         <v>1.360761358937363</v>
       </c>
-      <c r="Y32" s="7" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z32" s="7" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>Phase 5 pacdemons-only originally; Phase 11 added womenwork/neilang</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H33" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="8" t="n">
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>1707</v>
       </c>
-      <c r="K33" s="8" t="n">
+      <c r="L33" t="n">
         <v>0.02031732330670962</v>
       </c>
-      <c r="L33" s="8" t="n">
+      <c r="M33" t="n">
         <v>0.3214285714285715</v>
       </c>
-      <c r="M33" s="8" t="n">
+      <c r="N33" t="n">
         <v>0.1120238276689649</v>
       </c>
-      <c r="N33" s="8" t="n">
+      <c r="O33" t="n">
         <v>0.1611940298507463</v>
       </c>
-      <c r="O33" s="8" t="n">
+      <c r="P33" t="n">
         <v>0.1075697211155379</v>
       </c>
-      <c r="P33" s="8" t="n">
+      <c r="Q33" t="n">
         <v>0.5349653163219305</v>
       </c>
-      <c r="Q33" s="8" t="n">
+      <c r="R33" t="n">
         <v>0.09441603090185147</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="S33" t="n">
         <v>0.09783245459871118</v>
       </c>
-      <c r="S33" s="8" t="n">
+      <c r="T33" t="n">
         <v>0.09783245459871122</v>
       </c>
-      <c r="T33" s="8" t="n">
+      <c r="U33" t="n">
         <v>1.852958406561219</v>
       </c>
-      <c r="U33" s="8" t="n">
+      <c r="V33" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V33" s="8" t="n">
+      <c r="W33" t="n">
         <v>0.09783245459871104</v>
       </c>
-      <c r="W33" s="8" t="n"/>
-      <c r="X33" s="8" t="n"/>
-      <c r="Y33" s="7" t="inlineStr">
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z33" s="7" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Extended shortlist follow-up: C6 added post hoc to test the recall-driven candidate; not in original mean-rank shortlist.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="G34" t="n">
         <v>0.4</v>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H34" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="8" t="n">
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>1707</v>
       </c>
-      <c r="K34" s="8" t="n">
+      <c r="L34" t="n">
         <v>0.02229049611733434</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="M34" t="n">
         <v>0.4404761904761905</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="N34" t="n">
         <v>0.1817869469207549</v>
       </c>
-      <c r="N34" s="8" t="n">
+      <c r="O34" t="n">
         <v>0.2144927536231884</v>
       </c>
-      <c r="O34" s="8" t="n">
+      <c r="P34" t="n">
         <v>0.1417624521072797</v>
       </c>
-      <c r="P34" s="8" t="n">
+      <c r="Q34" t="n">
         <v>0.5630951874991146</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="R34" t="n">
         <v>0.1513025004265531</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="S34" t="n">
         <v>0.1036906854130053</v>
       </c>
-      <c r="S34" s="8" t="n">
+      <c r="T34" t="n">
         <v>0.1036906854130053</v>
       </c>
-      <c r="T34" s="8" t="n">
+      <c r="U34" t="n">
         <v>1.847100175746925</v>
       </c>
-      <c r="U34" s="8" t="n">
+      <c r="V34" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V34" s="8" t="n">
+      <c r="W34" t="n">
         <v>0.1036906854130051</v>
       </c>
-      <c r="W34" s="8" t="n"/>
-      <c r="X34" s="8" t="n"/>
-      <c r="Y34" s="7" t="inlineStr">
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z34" s="7" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Extended shortlist follow-up: C6 added post hoc to test the recall-driven candidate; not in original mean-rank shortlist.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="G35" t="n">
         <v>0.8</v>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H35" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="8" t="n">
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>1707</v>
       </c>
-      <c r="K35" s="8" t="n">
+      <c r="L35" t="n">
         <v>0.02788569764264068</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="M35" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="N35" t="n">
         <v>0.07107257867235156</v>
       </c>
-      <c r="N35" s="8" t="n">
+      <c r="O35" t="n">
         <v>0.1290322580645161</v>
       </c>
-      <c r="O35" s="8" t="n">
+      <c r="P35" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="P35" s="8" t="n">
+      <c r="Q35" t="n">
         <v>0.5112616911624356</v>
       </c>
-      <c r="Q35" s="8" t="n">
+      <c r="R35" t="n">
         <v>0.05719545872967169</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="S35" t="n">
         <v>0.1195079086115993</v>
       </c>
-      <c r="S35" s="8" t="n">
+      <c r="T35" t="n">
         <v>0.1195079086115993</v>
       </c>
-      <c r="T35" s="8" t="n">
+      <c r="U35" t="n">
         <v>1.831282952548331</v>
       </c>
-      <c r="U35" s="8" t="n">
+      <c r="V35" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V35" s="8" t="n">
+      <c r="W35" t="n">
         <v>0.1195079086115991</v>
       </c>
-      <c r="W35" s="8" t="n"/>
-      <c r="X35" s="8" t="n"/>
-      <c r="Y35" s="7" t="inlineStr">
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z35" s="7" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>Extended shortlist follow-up: C6 added post hoc to test the recall-driven candidate; not in original mean-rank shortlist.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Phase 5</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="G36" t="n">
         <v>0.4</v>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H36" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="8" t="n">
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>1707</v>
       </c>
-      <c r="K36" s="8" t="n">
+      <c r="L36" t="n">
         <v>0.0001785663992747161</v>
       </c>
-      <c r="L36" s="8" t="n">
+      <c r="M36" t="n">
         <v>0.5</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="N36" t="n">
         <v>0.4382073256900008</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="O36" t="n">
         <v>0.4666666666666667</v>
       </c>
-      <c r="O36" s="8" t="n">
+      <c r="P36" t="n">
         <v>0.4375</v>
       </c>
-      <c r="P36" s="8" t="n">
+      <c r="Q36" t="n">
         <v>0.7184910327767471</v>
       </c>
-      <c r="Q36" s="8" t="n">
+      <c r="R36" t="n">
         <v>0.4371213057994312</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="S36" t="n">
         <v>0.007029876977152898</v>
       </c>
-      <c r="S36" s="8" t="n">
+      <c r="T36" t="n">
         <v>0.007029876977152929</v>
       </c>
-      <c r="T36" s="8" t="n">
+      <c r="U36" t="n">
         <v>1.943760984182777</v>
       </c>
-      <c r="U36" s="8" t="n">
+      <c r="V36" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V36" s="8" t="n">
+      <c r="W36" t="n">
         <v>0.007029876977152849</v>
       </c>
-      <c r="W36" s="8" t="n"/>
-      <c r="X36" s="8" t="n"/>
-      <c r="Y36" s="7" t="inlineStr">
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_direct_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z36" s="7" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>Extended shortlist follow-up: C6 added post hoc to test the recall-driven candidate; not in original mean-rank shortlist.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Phase 5</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>C6</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="G37" t="n">
         <v>0.8</v>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H37" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="8" t="n">
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>1707</v>
       </c>
-      <c r="K37" s="8" t="n">
+      <c r="L37" t="n">
         <v>0.00020849767264709</v>
       </c>
-      <c r="L37" s="8" t="n">
+      <c r="M37" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="N37" t="n">
         <v>0.4121050540110467</v>
       </c>
-      <c r="N37" s="8" t="n">
+      <c r="O37" t="n">
         <v>0.4419889502762431</v>
       </c>
-      <c r="O37" s="8" t="n">
+      <c r="P37" t="n">
         <v>0.4123711340206185</v>
       </c>
-      <c r="P37" s="8" t="n">
+      <c r="Q37" t="n">
         <v>0.705374308110593</v>
       </c>
-      <c r="Q37" s="8" t="n">
+      <c r="R37" t="n">
         <v>0.4109187449388563</v>
       </c>
-      <c r="R37" s="8" t="n">
+      <c r="S37" t="n">
         <v>0.007615700058582309</v>
       </c>
-      <c r="S37" s="8" t="n">
+      <c r="T37" t="n">
         <v>0.007615700058582336</v>
       </c>
-      <c r="T37" s="8" t="n">
+      <c r="U37" t="n">
         <v>1.943175161101347</v>
       </c>
-      <c r="U37" s="8" t="n">
+      <c r="V37" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V37" s="8" t="n">
+      <c r="W37" t="n">
         <v>0.007615700058582142</v>
       </c>
-      <c r="W37" s="8" t="n"/>
-      <c r="X37" s="8" t="n"/>
-      <c r="Y37" s="8" t="inlineStr">
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z37" s="8" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>Extended shortlist follow-up: C6 added post hoc to test the recall-driven candidate; not in original mean-rank shortlist.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Phase 7</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Stage 3 — Cross-vendor</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>gpt-5.4-mini</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="G38" t="n">
         <v>0.8</v>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H38" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="9" t="n">
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>1707</v>
       </c>
-      <c r="K38" s="9" t="n">
+      <c r="L38" t="n">
         <v>0.0003494478566051</v>
       </c>
-      <c r="L38" s="9" t="n">
+      <c r="M38" t="n">
         <v>0.4404761904761904</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="N38" t="n">
         <v>0.367668506875579</v>
       </c>
-      <c r="N38" s="9" t="n">
+      <c r="O38" t="n">
         <v>0.4</v>
       </c>
-      <c r="O38" s="9" t="n">
+      <c r="P38" t="n">
         <v>0.3663366336633663</v>
       </c>
-      <c r="P38" s="9" t="n">
+      <c r="Q38" t="n">
         <v>0.682812016104057</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="R38" t="n">
         <v>0.3659307893865011</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="S38" t="n">
         <v>0.009958992384299901</v>
       </c>
-      <c r="S38" s="9" t="n">
+      <c r="T38" t="n">
         <v>0.009958992384299901</v>
       </c>
-      <c r="T38" s="9" t="n">
+      <c r="U38" t="n">
         <v>1.94083186877563</v>
       </c>
-      <c r="U38" s="9" t="n">
+      <c r="V38" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="W38" t="n">
         <v>0.0099589923842997</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="X38" t="n">
         <v>0.3656</v>
       </c>
-      <c r="X38" s="9" t="n"/>
-      <c r="Y38" s="9" t="inlineStr">
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
         <is>
           <t>stages/stage_3_cross_vendor/metrics/gpt54mini_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z38" s="9" t="n"/>
+      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Phase 8</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Stage 3 — Cross-vendor</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>claude-haiku-4-5-20251001</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="G39" t="n">
         <v>0.8</v>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H39" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="9" t="n">
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>1707</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="L39" t="n">
         <v>0.0105271351910458</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="M39" t="n">
         <v>0.1309523809523809</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="N39" t="n">
         <v>0.2772092584480833</v>
       </c>
-      <c r="N39" s="9" t="n">
+      <c r="O39" t="n">
         <v>0.2178217821782178</v>
       </c>
-      <c r="O39" s="9" t="n">
+      <c r="P39" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="P39" s="9" t="n">
+      <c r="Q39" t="n">
         <v>0.596988162444376</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="R39" t="n">
         <v>0.2046463895818957</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="S39" t="n">
         <v>0.0392501464557703</v>
       </c>
-      <c r="S39" s="9" t="n">
+      <c r="T39" t="n">
         <v>0.0392501464557703</v>
       </c>
-      <c r="T39" s="9" t="n">
+      <c r="U39" t="n">
         <v>1.9900410076157</v>
       </c>
-      <c r="U39" s="9" t="n">
+      <c r="V39" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V39" s="9" t="n">
+      <c r="W39" t="n">
         <v>0.0392501464557704</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="X39" t="n">
         <v>0.194</v>
       </c>
-      <c r="X39" s="9" t="n"/>
-      <c r="Y39" s="9" t="inlineStr">
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
         <is>
           <t>stages/stage_3_cross_vendor/metrics/claudehaiku_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z39" s="9" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>Womenwork/neilang halted — Anthropic budget exhausted</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Phase 9</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Stage 3 — Cross-vendor</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>gemini-2.5-flash-lite</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="G40" t="n">
         <v>0.8</v>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H40" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="9" t="n">
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>1703</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="L40" t="n">
         <v>0.0230924648134406</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="M40" t="n">
         <v>0.0119047619047619</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="N40" t="n">
         <v>0.1064152827894985</v>
       </c>
-      <c r="N40" s="9" t="n">
+      <c r="O40" t="n">
         <v>0.0235294117647058</v>
       </c>
-      <c r="O40" s="9" t="n">
+      <c r="P40" t="n">
         <v>1</v>
       </c>
-      <c r="P40" s="9" t="n">
+      <c r="Q40" t="n">
         <v>0.4992684698088811</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="R40" t="n">
         <v>0.0223948211111647</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="S40" t="n">
         <v>0.0487375220199647</v>
       </c>
-      <c r="S40" s="9" t="n">
+      <c r="T40" t="n">
         <v>0.0487375220199647</v>
       </c>
-      <c r="T40" s="9" t="n">
+      <c r="U40" t="n">
         <v>1.999412800939518</v>
       </c>
-      <c r="U40" s="9" t="n">
+      <c r="V40" t="n">
         <v>1.950675278919554</v>
       </c>
-      <c r="V40" s="9" t="n">
+      <c r="W40" t="n">
         <v>0.0487375220199646</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="X40" t="n">
         <v>-0.0015</v>
       </c>
-      <c r="X40" s="9" t="n"/>
-      <c r="Y40" s="9" t="inlineStr">
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
         <is>
           <t>stages/stage_3_cross_vendor/metrics/geminiflashlite_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z40" s="9" t="n"/>
+      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Phase 10</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Stage 3 — Cross-vendor</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>meta-llama/llama-3.3-70b-instruct</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="G41" t="n">
         <v>0.8</v>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H41" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="9" t="n">
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1707</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="L41" t="n">
         <v>0.0016719169902073</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="M41" t="n">
         <v>0.3095238095238095</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="N41" t="n">
         <v>0.3694131865971174</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="O41" t="n">
         <v>0.3823529411764705</v>
       </c>
-      <c r="O41" s="9" t="n">
+      <c r="P41" t="n">
         <v>0.5</v>
       </c>
-      <c r="P41" s="9" t="n">
+      <c r="Q41" t="n">
         <v>0.6783637799231956</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="R41" t="n">
         <v>0.3582017402513696</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="S41" t="n">
         <v>0.018746338605741</v>
       </c>
-      <c r="S41" s="9" t="n">
+      <c r="T41" t="n">
         <v>0.018746338605741</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="U41" t="n">
         <v>1.969537199765671</v>
       </c>
-      <c r="U41" s="9" t="n">
+      <c r="V41" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V41" s="9" t="n">
+      <c r="W41" t="n">
         <v>0.0187463386057411</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="X41" t="n">
         <v>0.3567</v>
       </c>
-      <c r="X41" s="9" t="n"/>
-      <c r="Y41" s="9" t="inlineStr">
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr">
         <is>
           <t>stages/stage_3_cross_vendor/metrics/llama3370b_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z41" s="9" t="n"/>
+      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Phase 6+13</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Stage 4 — Prompt design</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="G42" t="n">
         <v>0.8</v>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>sen</t>
         </is>
       </c>
-      <c r="H42" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I42" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="10" t="n">
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>1707</v>
       </c>
-      <c r="K42" s="10" t="n">
+      <c r="L42" t="n">
         <v>0.0002084976726471</v>
       </c>
-      <c r="L42" s="10" t="n">
+      <c r="M42" t="n">
         <v>0.4523809523809524</v>
       </c>
-      <c r="M42" s="10" t="n">
+      <c r="N42" t="n">
         <v>0.3887077505055303</v>
       </c>
-      <c r="N42" s="10" t="n">
+      <c r="O42" t="n">
         <v>0.4198895027624309</v>
       </c>
-      <c r="O42" s="10" t="n">
+      <c r="P42" t="n">
         <v>0.3917525773195876</v>
       </c>
-      <c r="P42" s="10" t="n">
+      <c r="Q42" t="n">
         <v>0.6937059638773491</v>
       </c>
-      <c r="Q42" s="10" t="n">
+      <c r="R42" t="n">
         <v>0.3875887942433654</v>
       </c>
-      <c r="R42" s="10" t="n">
+      <c r="S42" t="n">
         <v>0.0076157000585823</v>
       </c>
-      <c r="S42" s="10" t="n">
+      <c r="T42" t="n">
         <v>0.0076157000585823</v>
       </c>
-      <c r="T42" s="10" t="n">
+      <c r="U42" t="n">
         <v>1.943175161101348</v>
       </c>
-      <c r="U42" s="10" t="n">
+      <c r="V42" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V42" s="10" t="n">
+      <c r="W42" t="n">
         <v>0.0076157000585821</v>
       </c>
-      <c r="W42" s="10" t="n">
+      <c r="X42" t="n">
         <v>0.3874</v>
       </c>
-      <c r="X42" s="10" t="n">
+      <c r="Y42" t="n">
         <v>-1.478643567773325</v>
       </c>
-      <c r="Y42" s="10" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>stages/stage_4_prompt_design/metrics/sendili_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z42" s="10" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>Phase 6 spot-check is C7 row; Phase 13 added C1/C3/C4</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Phase 6+13</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Stage 4 — Prompt design</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="G43" t="n">
         <v>0.8</v>
       </c>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>sen</t>
         </is>
       </c>
-      <c r="H43" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I43" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="10" t="n">
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>1707</v>
       </c>
-      <c r="K43" s="10" t="n">
+      <c r="L43" t="n">
         <v>0.0002084976726471</v>
       </c>
-      <c r="L43" s="10" t="n">
+      <c r="M43" t="n">
         <v>0.4642857142857143</v>
       </c>
-      <c r="M43" s="10" t="n">
+      <c r="N43" t="n">
         <v>0.4004064022582885</v>
       </c>
-      <c r="N43" s="10" t="n">
+      <c r="O43" t="n">
         <v>0.430939226519337</v>
       </c>
-      <c r="O43" s="10" t="n">
+      <c r="P43" t="n">
         <v>0.4020618556701031</v>
       </c>
-      <c r="P43" s="10" t="n">
+      <c r="Q43" t="n">
         <v>0.699540135993971</v>
       </c>
-      <c r="Q43" s="10" t="n">
+      <c r="R43" t="n">
         <v>0.3992537695911109</v>
       </c>
-      <c r="R43" s="10" t="n">
+      <c r="S43" t="n">
         <v>0.0076157000585823</v>
       </c>
-      <c r="S43" s="10" t="n">
+      <c r="T43" t="n">
         <v>0.0076157000585823</v>
       </c>
-      <c r="T43" s="10" t="n">
+      <c r="U43" t="n">
         <v>1.943175161101348</v>
       </c>
-      <c r="U43" s="10" t="n">
+      <c r="V43" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V43" s="10" t="n">
+      <c r="W43" t="n">
         <v>0.0076157000585821</v>
       </c>
-      <c r="W43" s="10" t="n">
+      <c r="X43" t="n">
         <v>0.3991</v>
       </c>
-      <c r="X43" s="10" t="n">
+      <c r="Y43" t="n">
         <v>-3.141376572115183</v>
       </c>
-      <c r="Y43" s="10" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>stages/stage_4_prompt_design/metrics/sendili_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z43" s="10" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>Phase 6 spot-check is C7 row; Phase 13 added C1/C3/C4</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Phase 6+13</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Stage 4 — Prompt design</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="G44" t="n">
         <v>0.8</v>
       </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>sen</t>
         </is>
       </c>
-      <c r="H44" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I44" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="10" t="n">
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>1707</v>
       </c>
-      <c r="K44" s="10" t="n">
+      <c r="L44" t="n">
         <v>0.0012215701266699</v>
       </c>
-      <c r="L44" s="10" t="n">
+      <c r="M44" t="n">
         <v>0.5</v>
       </c>
-      <c r="M44" s="10" t="n">
+      <c r="N44" t="n">
         <v>0.3884737172073094</v>
       </c>
-      <c r="N44" s="10" t="n">
+      <c r="O44" t="n">
         <v>0.417910447761194</v>
       </c>
-      <c r="O44" s="10" t="n">
+      <c r="P44" t="n">
         <v>0.358974358974359</v>
       </c>
-      <c r="P44" s="10" t="n">
+      <c r="Q44" t="n">
         <v>0.6907479409674318</v>
       </c>
-      <c r="Q44" s="10" t="n">
+      <c r="R44" t="n">
         <v>0.3825370767133197</v>
       </c>
-      <c r="R44" s="10" t="n">
+      <c r="S44" t="n">
         <v>0.0193321616871704</v>
       </c>
-      <c r="S44" s="10" t="n">
+      <c r="T44" t="n">
         <v>0.0193321616871704</v>
       </c>
-      <c r="T44" s="10" t="n">
+      <c r="U44" t="n">
         <v>1.931458699472759</v>
       </c>
-      <c r="U44" s="10" t="n">
+      <c r="V44" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V44" s="10" t="n">
+      <c r="W44" t="n">
         <v>0.0193321616871704</v>
       </c>
-      <c r="W44" s="10" t="n">
+      <c r="X44" t="n">
         <v>0.3815</v>
       </c>
-      <c r="X44" s="10" t="n">
+      <c r="Y44" t="n">
         <v>2.312682559573399</v>
       </c>
-      <c r="Y44" s="10" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>stages/stage_4_prompt_design/metrics/sendili_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z44" s="10" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>Phase 6 spot-check is C7 row; Phase 13 added C1/C3/C4</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Phase 6+13</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Stage 4 — Prompt design</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F45" s="10" t="n">
+      <c r="G45" t="n">
         <v>0.8</v>
       </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>sen</t>
         </is>
       </c>
-      <c r="H45" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="10" t="n">
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>1707</v>
       </c>
-      <c r="K45" s="10" t="n">
+      <c r="L45" t="n">
         <v>0.0010232533456869</v>
       </c>
-      <c r="L45" s="10" t="n">
+      <c r="M45" t="n">
         <v>0.4880952380952381</v>
       </c>
-      <c r="M45" s="10" t="n">
+      <c r="N45" t="n">
         <v>0.3839342074710409</v>
       </c>
-      <c r="N45" s="10" t="n">
+      <c r="O45" t="n">
         <v>0.4141414141414141</v>
       </c>
-      <c r="O45" s="10" t="n">
+      <c r="P45" t="n">
         <v>0.3596491228070175</v>
       </c>
-      <c r="P45" s="10" t="n">
+      <c r="Q45" t="n">
         <v>0.6890358812000603</v>
       </c>
-      <c r="Q45" s="10" t="n">
+      <c r="R45" t="n">
         <v>0.3789495474133876</v>
       </c>
-      <c r="R45" s="10" t="n">
+      <c r="S45" t="n">
         <v>0.0175746924428822</v>
       </c>
-      <c r="S45" s="10" t="n">
+      <c r="T45" t="n">
         <v>0.0175746924428822</v>
       </c>
-      <c r="T45" s="10" t="n">
+      <c r="U45" t="n">
         <v>1.933216168717047</v>
       </c>
-      <c r="U45" s="10" t="n">
+      <c r="V45" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V45" s="10" t="n">
+      <c r="W45" t="n">
         <v>0.0175746924428821</v>
       </c>
-      <c r="W45" s="10" t="n">
+      <c r="X45" t="n">
         <v>0.3781</v>
       </c>
-      <c r="X45" s="10" t="n">
+      <c r="Y45" t="n">
         <v>2.307337580315109</v>
       </c>
-      <c r="Y45" s="10" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>stages/stage_4_prompt_design/metrics/sendili_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z45" s="10" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>Phase 6 spot-check is C7 row; Phase 13 added C1/C3/C4</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Phase 14</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Stage 4 — Prompt design</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="G46" t="n">
         <v>0.8</v>
       </c>
-      <c r="G46" s="10" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H46" s="10" t="b">
+      <c r="I46" t="b">
         <v>1</v>
       </c>
-      <c r="I46" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="10" t="n">
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>1707</v>
       </c>
-      <c r="K46" s="10" t="n">
+      <c r="L46" t="n">
         <v>0.0001020213844094</v>
       </c>
-      <c r="L46" s="10" t="n">
+      <c r="M46" t="n">
         <v>0.369047619047619</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="N46" t="n">
         <v>0.3153062248248216</v>
       </c>
-      <c r="N46" s="10" t="n">
+      <c r="O46" t="n">
         <v>0.3502824858757062</v>
       </c>
-      <c r="O46" s="10" t="n">
+      <c r="P46" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="P46" s="10" t="n">
+      <c r="Q46" t="n">
         <v>0.657377881800998</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="R46" t="n">
         <v>0.3148526255169886</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="S46" t="n">
         <v>0.0052724077328646</v>
       </c>
-      <c r="S46" s="10" t="n">
+      <c r="T46" t="n">
         <v>0.0052724077328647</v>
       </c>
-      <c r="T46" s="10" t="n">
+      <c r="U46" t="n">
         <v>1.945518453427065</v>
       </c>
-      <c r="U46" s="10" t="n">
+      <c r="V46" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V46" s="10" t="n">
+      <c r="W46" t="n">
         <v>0.0052724077328645</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="X46" t="n">
         <v>0.4236</v>
       </c>
-      <c r="X46" s="10" t="n"/>
-      <c r="Y46" s="10" t="inlineStr">
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr">
         <is>
           <t>stages/stage_4_prompt_design/metrics/explicitcot_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z46" s="10" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>Excluded — MCC −27%</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Phase 15</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Stage 4 — Prompt design</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F47" s="10" t="n">
+      <c r="G47" t="n">
         <v>0.8</v>
       </c>
-      <c r="G47" s="10" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H47" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="10" t="n">
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
         <v>1707</v>
       </c>
-      <c r="K47" s="10" t="n">
+      <c r="L47" t="n">
         <v>0.0010876807816224</v>
       </c>
-      <c r="L47" s="10" t="n">
+      <c r="M47" t="n">
         <v>0.5357142857142857</v>
       </c>
-      <c r="M47" s="10" t="n">
+      <c r="N47" t="n">
         <v>0.4250685745379349</v>
       </c>
-      <c r="N47" s="10" t="n">
+      <c r="O47" t="n">
         <v>0.4522613065326633</v>
       </c>
-      <c r="O47" s="10" t="n">
+      <c r="P47" t="n">
         <v>0.391304347826087</v>
       </c>
-      <c r="P47" s="10" t="n">
+      <c r="Q47" t="n">
         <v>0.7091788647748853</v>
       </c>
-      <c r="Q47" s="10" t="n">
+      <c r="R47" t="n">
         <v>0.4192300849322509</v>
       </c>
-      <c r="R47" s="10" t="n">
+      <c r="S47" t="n">
         <v>0.0181605155243116</v>
       </c>
-      <c r="S47" s="10" t="n">
+      <c r="T47" t="n">
         <v>0.0181605155243116</v>
       </c>
-      <c r="T47" s="10" t="n">
+      <c r="U47" t="n">
         <v>1.932630345635618</v>
       </c>
-      <c r="U47" s="10" t="n">
+      <c r="V47" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V47" s="10" t="n">
+      <c r="W47" t="n">
         <v>0.0181605155243116</v>
       </c>
-      <c r="W47" s="10" t="n">
+      <c r="X47" t="n">
         <v>0.4236</v>
       </c>
-      <c r="X47" s="10" t="n"/>
-      <c r="Y47" s="10" t="inlineStr">
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr">
         <is>
           <t>stages/stage_4_prompt_design/metrics/politicalcontext_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z47" s="10" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>Political context prepend on pacdemons C7 · Direct · T=0.8 · s0 (3-seed pilot). See Phase 15 s1, s2 rows for stability replication. Fixed protocol 3-seed: PC has neutral effect on pacdemons (Δjsd +0.0003, Δmcc -0.010, Δrecall_min +0.000).</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Phase 16</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Stage 4 — Prompt design</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F48" s="10" t="n">
+      <c r="G48" t="n">
         <v>0.8</v>
       </c>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H48" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="10" t="n">
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>1707</v>
       </c>
-      <c r="K48" s="10" t="n">
+      <c r="L48" t="n">
         <v>0.004051195454221917</v>
       </c>
-      <c r="L48" s="10" t="n">
+      <c r="M48" t="n">
         <v>0.4047619047619048</v>
       </c>
-      <c r="M48" s="10" t="n">
+      <c r="N48" t="n">
         <v>0.2571397188253375</v>
       </c>
-      <c r="N48" s="10" t="n">
+      <c r="O48" t="n">
         <v>0.293103448275862</v>
       </c>
-      <c r="O48" s="10" t="n">
+      <c r="P48" t="n">
         <v>0.2297297297297297</v>
       </c>
-      <c r="P48" s="10" t="n">
+      <c r="Q48" t="n">
         <v>0.6207817681354169</v>
       </c>
-      <c r="Q48" s="10" t="n">
+      <c r="R48" t="n">
         <v>0.2457484642741675</v>
       </c>
-      <c r="R48" s="10" t="n">
+      <c r="S48" t="n">
         <v>0.03749267721148213</v>
       </c>
-      <c r="S48" s="10" t="n">
+      <c r="T48" t="n">
         <v>0.03749267721148217</v>
       </c>
-      <c r="T48" s="10" t="n">
+      <c r="U48" t="n">
         <v>1.913298183948448</v>
       </c>
-      <c r="U48" s="10" t="n">
+      <c r="V48" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V48" s="10" t="n">
+      <c r="W48" t="n">
         <v>0.03749267721148208</v>
       </c>
-      <c r="W48" s="10" t="n"/>
-      <c r="X48" s="10" t="n"/>
-      <c r="Y48" s="10" t="inlineStr">
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr">
         <is>
           <t>stages/stage_4_prompt_design/natural_ablation_analysis/metrics_side_by_side.csv</t>
         </is>
       </c>
-      <c r="Z48" s="10" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>Ablation: personas rewritten as natural Turkish biographies (3rd person, no raw 0-10 scores) via gpt-4o-mini. Best-setup cell identical to final protocol; only persona format differs.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Phase 4b</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Stage 5 — Multi-seed stability</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F49" s="14" t="n">
+      <c r="G49" t="n">
         <v>0.4</v>
       </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H49" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I49" s="14" t="n">
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="14" t="n">
+      <c r="K49" t="n">
         <v>756</v>
       </c>
-      <c r="K49" s="14" t="n">
+      <c r="L49" t="n">
         <v>0.02047250418255253</v>
       </c>
-      <c r="L49" s="14" t="n">
+      <c r="M49" t="n">
         <v>0.35</v>
       </c>
-      <c r="M49" s="14" t="n">
+      <c r="N49" t="n">
         <v>0.1289060534365967</v>
       </c>
-      <c r="N49" s="14" t="n">
+      <c r="O49" t="n">
         <v>0.1794871794871795</v>
       </c>
-      <c r="O49" s="14" t="n">
+      <c r="P49" t="n">
         <v>0.1206896551724138</v>
       </c>
-      <c r="P49" s="14" t="n">
+      <c r="Q49" t="n">
         <v>0.5425459496255957</v>
       </c>
-      <c r="Q49" s="14" t="n">
+      <c r="R49" t="n">
         <v>0.1094095125901928</v>
       </c>
-      <c r="R49" s="14" t="n">
+      <c r="S49" t="n">
         <v>0.1005291005291005</v>
       </c>
-      <c r="S49" s="14" t="n">
+      <c r="T49" t="n">
         <v>0.1005291005291006</v>
       </c>
-      <c r="T49" s="14" t="n">
+      <c r="U49" t="n">
         <v>1.846560846560847</v>
       </c>
-      <c r="U49" s="14" t="n">
+      <c r="V49" t="n">
         <v>1.947089947089947</v>
       </c>
-      <c r="V49" s="14" t="n">
+      <c r="W49" t="n">
         <v>0.1005291005291005</v>
       </c>
-      <c r="W49" s="14" t="n">
+      <c r="X49" t="n">
         <v>0.1311</v>
       </c>
-      <c r="X49" s="14" t="n"/>
-      <c r="Y49" s="14" t="inlineStr">
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr">
         <is>
           <t>stages/stage_5_multiseed_stability/metrics/seed1_shortlist_vs_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z49" s="14" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>⚠ PARTIAL: 756/1707 — intentionally stopped probe (Phase 4b)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Phase 12</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Stage 5 — Multi-seed stability</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F50" s="14" t="n">
+      <c r="G50" t="n">
         <v>0.8</v>
       </c>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H50" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" s="14" t="n">
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="14" t="n">
+      <c r="K50" t="n">
         <v>1707</v>
       </c>
-      <c r="K50" s="14" t="n">
+      <c r="L50" t="n">
         <v>0.0009605324299166</v>
       </c>
-      <c r="L50" s="14" t="n">
+      <c r="M50" t="n">
         <v>0.4880952380952381</v>
       </c>
-      <c r="M50" s="14" t="n">
+      <c r="N50" t="n">
         <v>0.3860443474944591</v>
       </c>
-      <c r="N50" s="14" t="n">
+      <c r="O50" t="n">
         <v>0.416243654822335</v>
       </c>
-      <c r="O50" s="14" t="n">
+      <c r="P50" t="n">
         <v>0.3628318584070796</v>
       </c>
-      <c r="P50" s="14" t="n">
+      <c r="Q50" t="n">
         <v>0.6902480319495573</v>
       </c>
-      <c r="Q50" s="14" t="n">
+      <c r="R50" t="n">
         <v>0.3813170708646528</v>
       </c>
-      <c r="R50" s="14" t="n">
+      <c r="S50" t="n">
         <v>0.0169888693614528</v>
       </c>
-      <c r="S50" s="14" t="n">
+      <c r="T50" t="n">
         <v>0.0169888693614528</v>
       </c>
-      <c r="T50" s="14" t="n">
+      <c r="U50" t="n">
         <v>1.933801991798477</v>
       </c>
-      <c r="U50" s="14" t="n">
+      <c r="V50" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V50" s="14" t="n">
+      <c r="W50" t="n">
         <v>0.0169888693614528</v>
       </c>
-      <c r="W50" s="14" t="n">
+      <c r="X50" t="n">
         <v>0.3805</v>
       </c>
-      <c r="X50" s="14" t="n"/>
-      <c r="Y50" s="14" t="inlineStr">
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
         <is>
           <t>stages/stage_5_multiseed_stability/metrics/seed1_shortlist_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z50" s="14" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>Stability check for pacdemons C7</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Phase 12</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Stage 5 — Multi-seed stability</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F51" s="14" t="n">
+      <c r="G51" t="n">
         <v>0.8</v>
       </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H51" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" s="14" t="n">
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
         <v>2</v>
       </c>
-      <c r="J51" s="14" t="n">
+      <c r="K51" t="n">
         <v>1707</v>
       </c>
-      <c r="K51" s="14" t="n">
+      <c r="L51" t="n">
         <v>0.000621301316202</v>
       </c>
-      <c r="L51" s="14" t="n">
+      <c r="M51" t="n">
         <v>0.5119047619047619</v>
       </c>
-      <c r="M51" s="14" t="n">
+      <c r="N51" t="n">
         <v>0.4216214946881123</v>
       </c>
-      <c r="N51" s="14" t="n">
+      <c r="O51" t="n">
         <v>0.450261780104712</v>
       </c>
-      <c r="O51" s="14" t="n">
+      <c r="P51" t="n">
         <v>0.4018691588785046</v>
       </c>
-      <c r="P51" s="14" t="n">
+      <c r="Q51" t="n">
         <v>0.7088417184730821</v>
       </c>
-      <c r="Q51" s="14" t="n">
+      <c r="R51" t="n">
         <v>0.4181834117268982</v>
       </c>
-      <c r="R51" s="14" t="n">
+      <c r="S51" t="n">
         <v>0.0134739308728763</v>
       </c>
-      <c r="S51" s="14" t="n">
+      <c r="T51" t="n">
         <v>0.0134739308728764</v>
       </c>
-      <c r="T51" s="14" t="n">
+      <c r="U51" t="n">
         <v>1.937316930287053</v>
       </c>
-      <c r="U51" s="14" t="n">
+      <c r="V51" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V51" s="14" t="n">
+      <c r="W51" t="n">
         <v>0.0134739308728764</v>
       </c>
-      <c r="W51" s="14" t="n">
+      <c r="X51" t="n">
         <v>0.4177</v>
       </c>
-      <c r="X51" s="14" t="n"/>
-      <c r="Y51" s="14" t="inlineStr">
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr">
         <is>
           <t>stages/stage_5_multiseed_stability/metrics/seed2_shortlist_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z51" s="14" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>Stability check for pacdemons C7</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Phase 2/3</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F52" s="8" t="n">
+      <c r="G52" t="n">
         <v>0.4</v>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H52" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I52" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="8" t="n">
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>1707</v>
       </c>
-      <c r="K52" s="8" t="n">
+      <c r="L52" t="n">
         <v>0.0007828296536461819</v>
       </c>
-      <c r="L52" s="8" t="n">
+      <c r="M52" t="n">
         <v>0.4880952380952381</v>
       </c>
-      <c r="M52" s="8" t="n">
+      <c r="N52" t="n">
         <v>0.3925338659073562</v>
       </c>
-      <c r="N52" s="8" t="n">
+      <c r="O52" t="n">
         <v>0.422680412371134</v>
       </c>
-      <c r="O52" s="8" t="n">
+      <c r="P52" t="n">
         <v>0.3727272727272727</v>
       </c>
-      <c r="P52" s="8" t="n">
+      <c r="Q52" t="n">
         <v>0.6939489018377409</v>
       </c>
-      <c r="Q52" s="8" t="n">
+      <c r="R52" t="n">
         <v>0.388559476522173</v>
       </c>
-      <c r="R52" s="8" t="n">
+      <c r="S52" t="n">
         <v>0.01523140011716462</v>
       </c>
-      <c r="S52" s="8" t="n">
+      <c r="T52" t="n">
         <v>0.01523140011716462</v>
       </c>
-      <c r="T52" s="8" t="n">
+      <c r="U52" t="n">
         <v>1.935559461042765</v>
       </c>
-      <c r="U52" s="8" t="n">
+      <c r="V52" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V52" s="8" t="n">
+      <c r="W52" t="n">
         <v>0.01523140011716451</v>
       </c>
-      <c r="W52" s="8" t="n"/>
-      <c r="X52" s="8" t="n"/>
-      <c r="Y52" s="8" t="inlineStr">
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_direct_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z52" s="8" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>C11 · gpt-4o-mini · Direct · T=0.4 (Stage 2 grid extension; C11 added after Stage 1).</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Phase 2/3</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F53" s="8" t="n">
+      <c r="G53" t="n">
         <v>0.8</v>
       </c>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H53" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="8" t="n">
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
         <v>1707</v>
       </c>
-      <c r="K53" s="8" t="n">
+      <c r="L53" t="n">
         <v>0.0007271581029816624</v>
       </c>
-      <c r="L53" s="8" t="n">
+      <c r="M53" t="n">
         <v>0.4761904761904762</v>
       </c>
-      <c r="M53" s="8" t="n">
+      <c r="N53" t="n">
         <v>0.3836747942721034</v>
       </c>
-      <c r="N53" s="8" t="n">
+      <c r="O53" t="n">
         <v>0.4145077720207254</v>
       </c>
-      <c r="O53" s="8" t="n">
+      <c r="P53" t="n">
         <v>0.3669724770642202</v>
       </c>
-      <c r="P53" s="8" t="n">
+      <c r="Q53" t="n">
         <v>0.689712749717286</v>
       </c>
-      <c r="Q53" s="8" t="n">
+      <c r="R53" t="n">
         <v>0.3800487884836038</v>
       </c>
-      <c r="R53" s="8" t="n">
+      <c r="S53" t="n">
         <v>0.01464557703573521</v>
       </c>
-      <c r="S53" s="8" t="n">
+      <c r="T53" t="n">
         <v>0.01464557703573521</v>
       </c>
-      <c r="T53" s="8" t="n">
+      <c r="U53" t="n">
         <v>1.936145284124194</v>
       </c>
-      <c r="U53" s="8" t="n">
+      <c r="V53" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V53" s="8" t="n">
+      <c r="W53" t="n">
         <v>0.01464557703573521</v>
       </c>
-      <c r="W53" s="8" t="n"/>
-      <c r="X53" s="8" t="n"/>
-      <c r="Y53" s="8" t="inlineStr">
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z53" s="8" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>C11 · gpt-4o-mini · Direct · T=0.8 (Stage 2 grid extension; C11 added after Stage 1).</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Phase 2/3</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F54" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H54" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I54" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="8" t="n">
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>1707</v>
       </c>
-      <c r="K54" s="8" t="n">
+      <c r="L54" t="n">
         <v>0.02661003515915868</v>
       </c>
-      <c r="L54" s="8" t="n">
+      <c r="M54" t="n">
         <v>0.4404761904761905</v>
       </c>
-      <c r="M54" s="8" t="n">
+      <c r="N54" t="n">
         <v>0.168634814848922</v>
       </c>
-      <c r="N54" s="8" t="n">
+      <c r="O54" t="n">
         <v>0.2021857923497268</v>
       </c>
-      <c r="O54" s="8" t="n">
+      <c r="P54" t="n">
         <v>0.1312056737588652</v>
       </c>
-      <c r="P54" s="8" t="n">
+      <c r="Q54" t="n">
         <v>0.5531926337076718</v>
       </c>
-      <c r="Q54" s="8" t="n">
+      <c r="R54" t="n">
         <v>0.136723093389864</v>
       </c>
-      <c r="R54" s="8" t="n">
+      <c r="S54" t="n">
         <v>0.1159929701230228</v>
       </c>
-      <c r="S54" s="8" t="n">
+      <c r="T54" t="n">
         <v>0.1159929701230229</v>
       </c>
-      <c r="T54" s="8" t="n">
+      <c r="U54" t="n">
         <v>1.834797891036907</v>
       </c>
-      <c r="U54" s="8" t="n">
+      <c r="V54" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V54" s="8" t="n">
+      <c r="W54" t="n">
         <v>0.1159929701230227</v>
       </c>
-      <c r="W54" s="8" t="n"/>
-      <c r="X54" s="8" t="n"/>
-      <c r="Y54" s="8" t="inlineStr">
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T0_metrics.csv</t>
         </is>
       </c>
-      <c r="Z54" s="8" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>C11 · gpt-4o-mini · VS-CoT · T=0.0 (Stage 2 grid extension; C11 added after Stage 1). Fixed sampling.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Phase 2/3</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F55" s="8" t="n">
+      <c r="G55" t="n">
         <v>0.4</v>
       </c>
-      <c r="G55" s="8" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H55" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="8" t="n">
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
         <v>1707</v>
       </c>
-      <c r="K55" s="8" t="n">
+      <c r="L55" t="n">
         <v>0.02983216073579823</v>
       </c>
-      <c r="L55" s="8" t="n">
+      <c r="M55" t="n">
         <v>0.4642857142857143</v>
       </c>
-      <c r="M55" s="8" t="n">
+      <c r="N55" t="n">
         <v>0.1742077864924657</v>
       </c>
-      <c r="N55" s="8" t="n">
+      <c r="O55" t="n">
         <v>0.2047244094488189</v>
       </c>
-      <c r="O55" s="8" t="n">
+      <c r="P55" t="n">
         <v>0.1313131313131313</v>
       </c>
-      <c r="P55" s="8" t="n">
+      <c r="Q55" t="n">
         <v>0.5524116607085835</v>
       </c>
-      <c r="Q55" s="8" t="n">
+      <c r="R55" t="n">
         <v>0.1386411666841529</v>
       </c>
-      <c r="R55" s="8" t="n">
+      <c r="S55" t="n">
         <v>0.124780316344464</v>
       </c>
-      <c r="S55" s="8" t="n">
+      <c r="T55" t="n">
         <v>0.124780316344464</v>
       </c>
-      <c r="T55" s="8" t="n">
+      <c r="U55" t="n">
         <v>1.826010544815466</v>
       </c>
-      <c r="U55" s="8" t="n">
+      <c r="V55" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V55" s="8" t="n">
+      <c r="W55" t="n">
         <v>0.1247803163444638</v>
       </c>
-      <c r="W55" s="8" t="n"/>
-      <c r="X55" s="8" t="n"/>
-      <c r="Y55" s="8" t="inlineStr">
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T04_metrics.csv</t>
         </is>
       </c>
-      <c r="Z55" s="8" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>C11 · gpt-4o-mini · VS-CoT · T=0.4 (Stage 2 grid extension; C11 added after Stage 1). Fixed sampling.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Phase 2/3</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Stage 2 — Sampling &amp; temperature</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="D56" s="8" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>vs</t>
         </is>
       </c>
-      <c r="F56" s="8" t="n">
+      <c r="G56" t="n">
         <v>0.8</v>
       </c>
-      <c r="G56" s="8" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H56" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I56" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="8" t="n">
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>1707</v>
       </c>
-      <c r="K56" s="8" t="n">
+      <c r="L56" t="n">
         <v>0.03406604459615161</v>
       </c>
-      <c r="L56" s="8" t="n">
+      <c r="M56" t="n">
         <v>0.3928571428571428</v>
       </c>
-      <c r="M56" s="8" t="n">
+      <c r="N56" t="n">
         <v>0.1216804357123627</v>
       </c>
-      <c r="N56" s="8" t="n">
+      <c r="O56" t="n">
         <v>0.165</v>
       </c>
-      <c r="O56" s="8" t="n">
+      <c r="P56" t="n">
         <v>0.1044303797468354</v>
       </c>
-      <c r="P56" s="8" t="n">
+      <c r="Q56" t="n">
         <v>0.527091904445919</v>
       </c>
-      <c r="Q56" s="8" t="n">
+      <c r="R56" t="n">
         <v>0.09460515283177084</v>
       </c>
-      <c r="R56" s="8" t="n">
+      <c r="S56" t="n">
         <v>0.1359109548916227</v>
       </c>
-      <c r="S56" s="8" t="n">
+      <c r="T56" t="n">
         <v>0.1359109548916227</v>
       </c>
-      <c r="T56" s="8" t="n">
+      <c r="U56" t="n">
         <v>1.814879906268307</v>
       </c>
-      <c r="U56" s="8" t="n">
+      <c r="V56" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V56" s="8" t="n">
+      <c r="W56" t="n">
         <v>0.1359109548916226</v>
       </c>
-      <c r="W56" s="8" t="n"/>
-      <c r="X56" s="8" t="n"/>
-      <c r="Y56" s="8" t="inlineStr">
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr">
         <is>
           <t>stages/stage_2_sampling_and_temperature/metrics/shortlist_vs_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z56" s="8" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>C11 · gpt-4o-mini · VS-CoT · T=0.8 (Stage 2 grid extension; C11 added after Stage 1). Fixed sampling.</t>
         </is>
@@ -5779,78 +5967,85 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>0.8</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H57" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
         <v>1</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>1707</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>0.001153793353711993</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>0.5</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>0.390551511854037</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>0.42</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>0.3620689655172414</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>0.6919539514623522</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>0.3848877954223514</v>
       </c>
-      <c r="R57" t="n">
+      <c r="S57" t="n">
         <v>0.01874633860574106</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>0.01874633860574105</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>1.932044522554189</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>0.01874633860574093</v>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr">
         <is>
           <t>stages/stage_4_prompt_design/metrics/politicalcontext_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>Political context prepend on pacdemons C7 · Direct · T=0.8 · s1. 3-seed pilot symmetric to womenwork PC ablation.</t>
         </is>
@@ -5869,85 +6064,91 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>C7</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>0.8</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>ben</t>
         </is>
       </c>
-      <c r="H58" t="b">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
         <v>2</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>1707</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>0.001153793353711993</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>0.5</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>0.390551511854037</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>0.42</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>0.3620689655172414</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>0.6919539514623522</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>0.3848877954223514</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S58" t="n">
         <v>0.01874633860574106</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>0.01874633860574105</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>1.932044522554189</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>1.95079086115993</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>0.01874633860574093</v>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr">
         <is>
           <t>stages/stage_4_prompt_design/metrics/politicalcontext_direct_T08_metrics.csv</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>Political context prepend on pacdemons C7 · Direct · T=0.8 · s2. 3-seed pilot symmetric to womenwork PC ablation.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>